--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data_dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="silver_core_schema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="bronze_to_silver" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="document_control" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data_dictionary'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'silver_core_schema'!$A$1:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'bronze_to_silver'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'document_control'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,52 +448,2131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>raw_column</t>
+          <t>ordinal</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>silver_column</t>
+          <t>field_group</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>raw_type</t>
+          <t>column_name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>silver_type</t>
+          <t>data_type</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source_or_derivation</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>nullable</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Literal SRC01</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Stable catalog identifier for the source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Bronze source_name</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Current value vduydong/vietnam-real-estates-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>source_listing_id</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>NULL for SRC01</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Reserved for a native listing identifier from future listing sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>source_record_url</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>NULL for SRC01</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Reserved for a source listing URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>listing_id</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 under the versioned ID contract</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Source-scoped content identity; exact duplicate audit rows share this value</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>listing_id_version</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Literal src_content_sha256_v1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Version of the listing ID contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>duplicate_group_id</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Equal to listing_id in v1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Exact intra-source duplicate group</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>duplicate_count</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>COUNT over duplicate_group_id</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Number of audit rows in the exact duplicate group</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>duplicate_rank</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ROW_NUMBER over duplicate_group_id</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Rank 1 is the canonical business row</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>is_canonical</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>duplicate_rank = 1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Required filter for analytical counts and measures</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(Bronze name), '')</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Canonical listing title</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Trim outer whitespace; blank becomes NULL</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Canonical listing description</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>property_type_raw</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Bronze property_type_name unchanged</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Raw property type for audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>property_type</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Trim and map to one of the five reviewed SRC01 categories</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Canonical property type</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>province_name_raw</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Bronze province_name unchanged</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Source province label before location mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>province_name</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(province_name_raw), '')</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Clean display label only; not a master-data match</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>district_name_raw</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Bronze district_name unchanged</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Source district label before location mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>district_name</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(district_name_raw), '')</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Clean display label only; not a master-data match</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>ward_name_raw</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Bronze ward_name unchanged</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Source ward label before location mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ward_name</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(ward_name_raw), '')</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Clean display label only; not a master-data match</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>street_name</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(Bronze street_name), '')</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Clean source street label</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>project_name</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(Bronze project_name), '')</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Clean source project label</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>price_raw</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Bronze price unchanged</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Preserved raw value for cast audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>price_vnd</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>decimal(20,0)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>TRY_CAST(TRIM(price_raw)); zero retained for audit</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Listing/asking price in VND; not a completed transaction price</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>area_m2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Bronze area</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Area in square metres; invalid values remain auditable through DQ flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>price_per_m2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>decimal(24,2)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>price_vnd / area_m2 only when price_vnd &gt; 0 and area_m2 &gt; 0</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Derived asking price per square metre</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>floor_count</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Cast Bronze floor_count after integer/nonnegative precondition check</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Number of floors</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>frontage_width_m</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Bronze frontage_width</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Frontage width in metres</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>house_depth_m</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Bronze house_depth</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>House depth in metres</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>road_width_m</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Bronze road_width</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Road width in metres</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>bedroom_count</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Cast Bronze bedroom_count after integer/nonnegative precondition check</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>bathroom_count</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Cast Bronze bathroom_count after integer/nonnegative precondition check</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Number of bathrooms</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>house_direction</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(Bronze house_direction), '')</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Clean source house direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>balcony_direction</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>NULLIF(TRIM(Bronze balcony_direction), '')</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Clean source balcony direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>published_at_raw</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Bronze published_at unchanged</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Preserved source timestamp without an observed UTC offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>published_at</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>timestamp_ntz</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Parse published_at_raw without timezone conversion</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Source-local-naive timestamp pending timezone confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>published_date</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>DATE(published_at)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Calendar date without timezone conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>published_year</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>YEAR(published_at)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Publication year</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>published_month</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>MONTH(published_at)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Publication month number</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>DATE_FORMAT(published_at, 'yyyy-MM')</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Business month used by downstream analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Bronze source_file</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Raw shard lineage</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>bronze_batch_id</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Bronze batch_id</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Bronze ingestion batch lineage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>bronze_ingested_at</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Bronze ingested_at</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>UTC technical ingestion timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>bronze_ingestion_date</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Bronze ingestion_date</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>UTC technical ingestion date</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>silver_batch_id</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Generated once per Silver execution</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Silver processing batch identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>silver_processed_at</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Generated once per Silver execution</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>UTC technical processing timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>lineage</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>silver_schema_version</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Literal silver_listing_core_v1</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Version of this output schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>dq_rule_version</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Literal src01_silver_core_dq_v1</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Version of the implemented DQ rule contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>dq_threshold_version</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Literal src01_raw_20260904_p99_v1</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Version of profiling-derived thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>dq_status</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Precedence REJECTED then REVIEW then VALID</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Row-level summary; not a universal Gold filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>dq_error_codes</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>array&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Sorted distinct DQ01-DQ14 codes; [] when valid</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Rule-specific failures/review flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>is_price_valid</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>price_vnd &gt; 0 and cast succeeded</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Usability flag for price KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>is_area_valid</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>area_m2 IS NOT NULL AND area_m2 &gt; 0</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Usability flag for area and price-per-m2 KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>is_published_at_valid</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>published_at parsed successfully</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Usability flag for time KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>is_province_valid</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>province_name IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Usability flag for province-level KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>is_district_valid</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>district_name IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Usability flag for district-level KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>is_ward_valid</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>ward_name IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Usability flag for ward-level KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>partition</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>partition_year_month</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>COALESCE(year_month, 'unknown')</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Physical partition key; pending user approval</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G59"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bronze_column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bronze_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>silver_output_columns</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>transformation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>audit_note</t>
         </is>
       </c>
     </row>
@@ -501,32 +2584,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>NULLIF(TRIM(name), '')</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiêu đề tin đăng</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Trim khoảng trắng</t>
+          <t>Raw value remains in immutable Bronze and participates in listing_id hash</t>
         </is>
       </c>
     </row>
@@ -538,32 +2611,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Trim outer whitespace; blank becomes NULL</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nội dung mô tả bất động sản</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Giữ nguyên, trim</t>
+          <t>Raw value remains in Bronze and participates in hash</t>
         </is>
       </c>
     </row>
@@ -575,32 +2638,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>property_type_raw; property_type</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Preserve raw; trim/map to five reviewed SRC01 categories</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Loại hình bất động sản</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa category</t>
+          <t>A new category is schema drift and must stop for review</t>
         </is>
       </c>
     </row>
@@ -612,32 +2665,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>province_name</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>province_name_raw; province_name</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Preserve raw; trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tỉnh/thành phố</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa tên địa phương</t>
+          <t>No administrative-code mapping in Silver Core</t>
         </is>
       </c>
     </row>
@@ -649,32 +2692,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>district_name</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>district_name_raw; district_name</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Preserve raw; trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Quận/huyện</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Trim, cho phép null</t>
+          <t>No administrative-code mapping in Silver Core</t>
         </is>
       </c>
     </row>
@@ -686,32 +2719,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ward_name</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>ward_name_raw; ward_name</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Preserve raw; trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Phường/xã</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Trim, cho phép null</t>
+          <t>No administrative-code mapping in Silver Core</t>
         </is>
       </c>
     </row>
@@ -723,32 +2746,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>street_name</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tên đường</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Trim</t>
+          <t>Raw value remains in Bronze and participates in hash</t>
         </is>
       </c>
     </row>
@@ -760,32 +2773,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>project_name</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tên dự án</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Trim</t>
+          <t>Raw value remains in Bronze and participates in hash</t>
         </is>
       </c>
     </row>
@@ -797,32 +2800,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>price_raw; price_vnd; price_per_m2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>decimal(20,0)</t>
+          <t>Preserve raw; TRY_CAST to DECIMAL(20,0); derive price/m2 only when price &gt; 0 and area &gt; 0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Giá bất động sản, đơn vị VND</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Cast string sang numeric</t>
+          <t>Listing/asking price in VND, not a completed transaction price</t>
         </is>
       </c>
     </row>
@@ -834,32 +2827,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>area_m2</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>area_m2; price_per_m2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>Rename; retain source value; validate positivity; derive price/m2 only when valid</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Diện tích bất động sản, đơn vị m²</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Validate và kiểm tra outlier</t>
+          <t>P99 area is REVIEW rather than deletion</t>
         </is>
       </c>
     </row>
@@ -871,32 +2854,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>floor_count</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Validate nonnegative integer precondition then cast INT</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Số tầng</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Validate và cast integer</t>
+          <t>P99 threshold is property-type-specific</t>
         </is>
       </c>
     </row>
@@ -908,32 +2881,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>frontage_width_m</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>Rename without unit conversion</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Chiều rộng mặt tiền, mét</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Validate</t>
+          <t>Raw value remains available in Bronze</t>
         </is>
       </c>
     </row>
@@ -945,32 +2908,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>house_depth_m</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>Rename without unit conversion</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chiều sâu bất động sản, mét</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Validate</t>
+          <t>Raw value remains available in Bronze</t>
         </is>
       </c>
     </row>
@@ -982,32 +2935,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>road_width_m</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>Rename without unit conversion</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chiều rộng đường, mét</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Validate</t>
+          <t>Raw value remains available in Bronze</t>
         </is>
       </c>
     </row>
@@ -1019,32 +2962,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>bedroom_count</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Validate nonnegative integer precondition then cast INT</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Số phòng ngủ</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Validate và cast integer</t>
+          <t>P99 threshold is property-type-specific</t>
         </is>
       </c>
     </row>
@@ -1056,32 +2989,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>bathroom_count</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Validate nonnegative integer precondition then cast INT</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Số phòng tắm</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Validate và cast integer</t>
+          <t>P99 threshold is property-type-specific</t>
         </is>
       </c>
     </row>
@@ -1093,32 +3016,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>house_direction</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hướng nhà</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa category</t>
+          <t>Raw value remains in Bronze and participates in hash</t>
         </is>
       </c>
     </row>
@@ -1130,32 +3043,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>balcony_direction</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Trim and convert blank to NULL</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Hướng ban công</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa category</t>
+          <t>Raw value remains in Bronze and participates in hash</t>
         </is>
       </c>
     </row>
@@ -1167,333 +3070,285 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>published_at</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>published_at_raw; published_at; published_date; published_year; published_month; year_month; partition_year_month</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>Preserve raw; parse TIMESTAMP_NTZ; derive calendar fields without timezone conversion</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Thời gian đăng tin</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Cast string sang timestamp</t>
+          <t>Timezone is an open approval decision</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>source_name</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>listing_id</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>source_name</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Preserve exact technical value vduydong/vietnam-real-estates-2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ID nội bộ của bản ghi</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Sinh ID từ dữ liệu nguồn</t>
+          <t>Included in listing_id and duplicate_group_id hash</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>source_file</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>price_per_m2</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>source_file</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>Preserve</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Giá trên mỗi mét vuông</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>price / area_m2</t>
+          <t>Used as the available duplicate ranking preference</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ingested_at</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>published_date</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>bronze_ingested_at</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Rename; preserve UTC technical timestamp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ngày đăng tin</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Tách từ published_at</t>
+          <t>Bronze lineage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ingestion_date</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>bronze_ingestion_date</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Năm đăng tin</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tách từ published_at</t>
+          <t>Bronze lineage</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>batch_id</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>bronze_batch_id</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tháng đăng tin</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Tách từ published_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>year_month</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tháng phân tích dạng YYYY-MM</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Tạo từ published_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>dq_status</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Trạng thái chất lượng dữ liệu</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>VALID / REVIEW / REJECTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>dq_error_codes</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Danh sách mã lỗi chất lượng dữ liệu</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Sinh từ Data Quality Rules</t>
+          <t>Bronze lineage</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:E25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED_AND_VALIDATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>silver_listing_core_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>source_scope</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SRC01 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>bronze_input_columns</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>silver_output_columns</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>schema_source</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>docs/silver/silver_core_schema.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>design_source</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>docs/silver/silver_core_design_proposal.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>implementation_status</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Implemented by src/silver/01_build_silver_core.py and independently validated</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>